--- a/data/satisfaction_detail/2026/1-8月/旅行社工作人员.xlsx
+++ b/data/satisfaction_detail/2026/1-8月/旅行社工作人员.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.960000000000001</v>
+        <v>9.952187500000001</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.960000000000001</v>
+        <v>9.952187500000001</v>
       </c>
     </row>
     <row r="3">
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>9.91</v>
+        <v>9.901718750000001</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>9.91</v>
+        <v>9.901718750000001</v>
       </c>
     </row>
     <row r="12">
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>9.73</v>
+        <v>9.80078125</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.73</v>
+        <v>9.80078125</v>
       </c>
     </row>
     <row r="13">
